--- a/OUTPUT/reverse_Q9PH24_Xylella_fastidiosa_9a5c.xlsx
+++ b/OUTPUT/reverse_Q9PH24_Xylella_fastidiosa_9a5c.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TTAGTA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TACTAA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ATGATT</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.0008</v>
+        <v>0.0009996001599360256</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TTA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TAA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ATT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.7474</v>
+        <v>0.7473010795681727</v>
       </c>
     </row>
     <row r="4">
@@ -540,11 +540,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
     <row r="5">
@@ -569,11 +569,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
     <row r="6">
@@ -598,11 +598,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
   </sheetData>
